--- a/data/material_avalibility.xlsx
+++ b/data/material_avalibility.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shubham82.Sharma\Documents\Projects\Kutchh New\Logistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9070596D-B60C-431F-AD91-6B14C642ED94}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F115F3AA-D393-4C30-B712-416A7B4993E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,23 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Planner tool Input'!$A$1:$I$92</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -129,7 +145,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -471,19 +487,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I92"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="28.33203125" customWidth="1"/>
-    <col min="2" max="2" width="37.77734375" customWidth="1"/>
-    <col min="3" max="3" width="31.33203125" customWidth="1"/>
+    <col min="1" max="1" width="28.28515625" customWidth="1"/>
+    <col min="2" max="2" width="37.7109375" customWidth="1"/>
+    <col min="3" max="3" width="31.28515625" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="36.109375" customWidth="1"/>
-    <col min="8" max="8" width="18.5546875" customWidth="1"/>
+    <col min="7" max="7" width="36.140625" customWidth="1"/>
+    <col min="8" max="8" width="18.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -509,7 +525,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9">
       <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
@@ -517,7 +533,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>5000090945</v>
       </c>
@@ -544,7 +560,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>5000090927</v>
       </c>
@@ -571,7 +587,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>5000090953</v>
       </c>
@@ -598,7 +614,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>5000090953</v>
       </c>
@@ -615,7 +631,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>5000090956</v>
       </c>
@@ -642,7 +658,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>5000090956</v>
       </c>
@@ -659,7 +675,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>5000090956</v>
       </c>
@@ -673,7 +689,7 @@
         <v>46212</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>5000090956</v>
       </c>
@@ -687,7 +703,7 @@
         <v>46221</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>5000091825</v>
       </c>
@@ -704,7 +720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>5000091825</v>
       </c>
@@ -718,7 +734,7 @@
         <v>46224</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>5000090952</v>
       </c>
@@ -734,11 +750,17 @@
       <c r="F13" s="1">
         <v>46190</v>
       </c>
+      <c r="G13">
+        <v>378</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
       <c r="I13" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>5000090952</v>
       </c>
@@ -754,11 +776,17 @@
       <c r="F14" s="1">
         <v>46195</v>
       </c>
+      <c r="G14">
+        <v>1512</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
       <c r="I14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>5000090952</v>
       </c>
@@ -774,11 +802,17 @@
       <c r="F15" s="1">
         <v>46192</v>
       </c>
+      <c r="G15">
+        <v>156</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
       <c r="I15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>5000090952</v>
       </c>
@@ -795,7 +829,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9">
       <c r="A17">
         <v>5000090952</v>
       </c>
@@ -812,7 +846,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9">
       <c r="A18">
         <v>5000090952</v>
       </c>
@@ -829,7 +863,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9">
       <c r="A19">
         <v>5000090952</v>
       </c>
@@ -846,7 +880,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9">
       <c r="A20">
         <v>5000090952</v>
       </c>
@@ -863,7 +897,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9">
       <c r="A21">
         <v>5000090952</v>
       </c>
@@ -880,7 +914,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9">
       <c r="A22">
         <v>5000090952</v>
       </c>
@@ -897,7 +931,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9">
       <c r="A23">
         <v>5000090952</v>
       </c>
@@ -914,7 +948,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9">
       <c r="A24">
         <v>5000090952</v>
       </c>
@@ -931,7 +965,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9">
       <c r="A25">
         <v>5000090952</v>
       </c>
@@ -945,7 +979,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9">
       <c r="A26">
         <v>5000090952</v>
       </c>
@@ -959,7 +993,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9">
       <c r="A27">
         <v>5000090952</v>
       </c>
@@ -976,7 +1010,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9">
       <c r="A28">
         <v>5000090952</v>
       </c>
@@ -990,7 +1024,7 @@
         <v>46212</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9">
       <c r="A29">
         <v>5000090952</v>
       </c>
@@ -1004,7 +1038,7 @@
         <v>46224</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9">
       <c r="A30">
         <v>5000090952</v>
       </c>
@@ -1015,7 +1049,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9">
       <c r="A31">
         <v>5000090929</v>
       </c>
@@ -1031,11 +1065,17 @@
       <c r="F31" s="1">
         <v>46190</v>
       </c>
+      <c r="G31">
+        <v>308</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
       <c r="I31" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9">
       <c r="A32">
         <v>5000090929</v>
       </c>
@@ -1051,11 +1091,17 @@
       <c r="F32" s="1">
         <v>46192</v>
       </c>
+      <c r="G32">
+        <v>156</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
       <c r="I32" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9">
       <c r="A33">
         <v>5000090929</v>
       </c>
@@ -1069,7 +1115,7 @@
         <v>46221</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9">
       <c r="A34">
         <v>5000090929</v>
       </c>
@@ -1083,7 +1129,7 @@
         <v>46224</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9">
       <c r="A35">
         <v>5000090929</v>
       </c>
@@ -1094,7 +1140,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9">
       <c r="A36">
         <v>5000091794</v>
       </c>
@@ -1105,7 +1151,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9">
       <c r="A37">
         <v>5000090928</v>
       </c>
@@ -1122,7 +1168,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9">
       <c r="A38">
         <v>5000090928</v>
       </c>
@@ -1139,7 +1185,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9">
       <c r="A39">
         <v>5000090928</v>
       </c>
@@ -1156,7 +1202,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9">
       <c r="A40">
         <v>5000090928</v>
       </c>
@@ -1173,7 +1219,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9">
       <c r="A41">
         <v>5000090928</v>
       </c>
@@ -1187,7 +1233,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9">
       <c r="A42">
         <v>5000090928</v>
       </c>
@@ -1201,7 +1247,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9">
       <c r="A43">
         <v>5000090928</v>
       </c>
@@ -1218,7 +1264,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9">
       <c r="A44">
         <v>5000090928</v>
       </c>
@@ -1232,7 +1278,7 @@
         <v>46212</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9">
       <c r="A45">
         <v>5000090928</v>
       </c>
@@ -1246,7 +1292,7 @@
         <v>46221</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9">
       <c r="A46">
         <v>5000090928</v>
       </c>
@@ -1260,7 +1306,7 @@
         <v>46224</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9">
       <c r="A47">
         <v>5000090928</v>
       </c>
@@ -1271,7 +1317,7 @@
         <v>25515</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9">
       <c r="B48" t="s">
         <v>23</v>
       </c>
@@ -1285,7 +1331,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9">
       <c r="A49">
         <v>5000090960</v>
       </c>
@@ -1302,7 +1348,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9">
       <c r="A50">
         <v>5000090960</v>
       </c>
@@ -1313,7 +1359,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9">
       <c r="A51">
         <v>5000090950</v>
       </c>
@@ -1327,7 +1373,7 @@
         <v>46212</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9">
       <c r="A52">
         <v>5000090950</v>
       </c>
@@ -1341,7 +1387,7 @@
         <v>46221</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9">
       <c r="A53">
         <v>5000090950</v>
       </c>
@@ -1355,7 +1401,7 @@
         <v>46224</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9">
       <c r="A54">
         <v>5000090957</v>
       </c>
@@ -1372,7 +1418,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9">
       <c r="A55">
         <v>5000090957</v>
       </c>
@@ -1389,7 +1435,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9">
       <c r="A56">
         <v>5000090957</v>
       </c>
@@ -1406,7 +1452,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9">
       <c r="A57">
         <v>5000090957</v>
       </c>
@@ -1423,7 +1469,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9">
       <c r="A58">
         <v>5000090957</v>
       </c>
@@ -1440,7 +1486,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9">
       <c r="A59">
         <v>5000090957</v>
       </c>
@@ -1457,7 +1503,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9">
       <c r="A60">
         <v>5000090957</v>
       </c>
@@ -1474,7 +1520,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9">
       <c r="A61">
         <v>5000090957</v>
       </c>
@@ -1491,7 +1537,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9">
       <c r="A62">
         <v>5000090957</v>
       </c>
@@ -1508,7 +1554,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9">
       <c r="A63">
         <v>5000090957</v>
       </c>
@@ -1522,7 +1568,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9">
       <c r="A64">
         <v>5000090957</v>
       </c>
@@ -1536,7 +1582,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9">
       <c r="A65">
         <v>5000090957</v>
       </c>
@@ -1553,7 +1599,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9">
       <c r="A66">
         <v>5000090957</v>
       </c>
@@ -1567,7 +1613,7 @@
         <v>46212</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9">
       <c r="A67">
         <v>5000090926</v>
       </c>
@@ -1583,11 +1629,17 @@
       <c r="F67" s="1">
         <v>46190</v>
       </c>
+      <c r="G67">
+        <v>252</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
       <c r="I67" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9">
       <c r="A68">
         <v>5000090926</v>
       </c>
@@ -1603,11 +1655,17 @@
       <c r="F68" s="1">
         <v>46195</v>
       </c>
+      <c r="G68">
+        <v>504</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
       <c r="I68" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9">
       <c r="A69">
         <v>5000090926</v>
       </c>
@@ -1623,11 +1681,17 @@
       <c r="F69" s="1">
         <v>46192</v>
       </c>
+      <c r="G69">
+        <v>252</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
       <c r="I69" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9">
       <c r="A70">
         <v>5000090926</v>
       </c>
@@ -1644,7 +1708,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9">
       <c r="B71" t="s">
         <v>28</v>
       </c>
@@ -1652,7 +1716,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9">
       <c r="A72">
         <v>5000090955</v>
       </c>
@@ -1666,7 +1730,7 @@
         <v>46212</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9">
       <c r="A73">
         <v>5000090955</v>
       </c>
@@ -1680,7 +1744,7 @@
         <v>46221</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9">
       <c r="A74">
         <v>5000090954</v>
       </c>
@@ -1697,7 +1761,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9">
       <c r="A75">
         <v>5000090954</v>
       </c>
@@ -1714,7 +1778,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9">
       <c r="A76">
         <v>5000090954</v>
       </c>
@@ -1728,7 +1792,7 @@
         <v>46197</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9">
       <c r="A77">
         <v>5000090954</v>
       </c>
@@ -1742,7 +1806,7 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9">
       <c r="A78">
         <v>5000090954</v>
       </c>
@@ -1756,7 +1820,7 @@
         <v>46212</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9">
       <c r="A79">
         <v>5000090951</v>
       </c>
@@ -1772,11 +1836,17 @@
       <c r="F79" s="1">
         <v>46139</v>
       </c>
+      <c r="G79">
+        <v>635</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
       <c r="I79" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9">
       <c r="A80">
         <v>5000090951</v>
       </c>
@@ -1792,11 +1862,17 @@
       <c r="F80" s="1">
         <v>46190</v>
       </c>
+      <c r="G80">
+        <v>540</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
       <c r="I80" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9">
       <c r="A81">
         <v>5000090951</v>
       </c>
@@ -1812,11 +1888,17 @@
       <c r="F81" s="1">
         <v>46195</v>
       </c>
+      <c r="G81">
+        <v>864</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
       <c r="I81" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9">
       <c r="A82">
         <v>5000090951</v>
       </c>
@@ -1832,11 +1914,17 @@
       <c r="F82" s="1">
         <v>46192</v>
       </c>
+      <c r="G82">
+        <v>642</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
       <c r="I82" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9">
       <c r="A83">
         <v>5000090951</v>
       </c>
@@ -1853,7 +1941,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9">
       <c r="A84">
         <v>5000090951</v>
       </c>
@@ -1870,7 +1958,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9">
       <c r="A85">
         <v>5000090951</v>
       </c>
@@ -1887,7 +1975,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9">
       <c r="A86">
         <v>5000090951</v>
       </c>
@@ -1904,7 +1992,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9">
       <c r="A87">
         <v>5000090951</v>
       </c>
@@ -1921,7 +2009,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9">
       <c r="A88">
         <v>5000090951</v>
       </c>
@@ -1938,7 +2026,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9">
       <c r="A89">
         <v>5000090951</v>
       </c>
@@ -1955,7 +2043,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9">
       <c r="A90">
         <v>5000090951</v>
       </c>
@@ -1972,7 +2060,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9">
       <c r="A91">
         <v>5000090951</v>
       </c>
@@ -1989,7 +2077,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9">
       <c r="A92">
         <v>5000090951</v>
       </c>
@@ -2012,87 +2100,87 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B088DB1E-FEB8-428B-9DA8-69DDD53FA0D4}">
   <dimension ref="B5:B21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="28.5546875" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:2">
       <c r="B5">
         <v>5000090945</v>
       </c>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:2">
       <c r="B6">
         <v>5000090927</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:2">
       <c r="B7">
         <v>5000090953</v>
       </c>
     </row>
-    <row r="8" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:2">
       <c r="B8">
         <v>5000090956</v>
       </c>
     </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:2">
       <c r="B9">
         <v>5000091825</v>
       </c>
     </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:2">
       <c r="B10">
         <v>5000090952</v>
       </c>
     </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:2">
       <c r="B11">
         <v>5000090929</v>
       </c>
     </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:2">
       <c r="B12">
         <v>5000091794</v>
       </c>
     </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:2">
       <c r="B13">
         <v>5000090928</v>
       </c>
     </row>
-    <row r="15" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:2">
       <c r="B15">
         <v>5000090960</v>
       </c>
     </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:2">
       <c r="B16">
         <v>5000090950</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:2">
       <c r="B17">
         <v>5000090957</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:2">
       <c r="B18">
         <v>5000090926</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:2">
       <c r="B19">
         <v>5000090955</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:2">
       <c r="B20">
         <v>5000090954</v>
       </c>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:2">
       <c r="B21">
         <v>5000090951</v>
       </c>

--- a/data/material_avalibility.xlsx
+++ b/data/material_avalibility.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shubham82.Sharma\Documents\Projects\Kutchh New\Logistics\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sahil2.Qureshi\Documents\Project_Planner_SHP\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F115F3AA-D393-4C30-B712-416A7B4993E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7754EF-2A41-4CF3-82FE-2F00271456EB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,23 +24,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="46">
   <si>
     <t>Item Code</t>
   </si>
@@ -136,19 +125,65 @@
   </si>
   <si>
     <t>PVC SHEET PILE 735X300X12X5500</t>
+  </si>
+  <si>
+    <t>PVC SHEET PILE MA450X138X4X2600</t>
+  </si>
+  <si>
+    <t>Added from Data (H-Lot-01)</t>
+  </si>
+  <si>
+    <t>Added from Data (H-Lot-03)</t>
+  </si>
+  <si>
+    <t>Added from Data (H-Lot-05)</t>
+  </si>
+  <si>
+    <t>Added from Data (H-Lot-06)</t>
+  </si>
+  <si>
+    <t>Added from Data (Z-Lot-29)</t>
+  </si>
+  <si>
+    <t>Added from Data (Z-Lot-31)</t>
+  </si>
+  <si>
+    <t>Added from Data (Z-Lot-32)</t>
+  </si>
+  <si>
+    <t>PVC SHEET PILE MA765X304X12X6250</t>
+  </si>
+  <si>
+    <t>Added from Data (H-Lot-02)</t>
+  </si>
+  <si>
+    <t>Added from Data (H-Lot-04)</t>
+  </si>
+  <si>
+    <t>PVC SHEET PILE MA765X280X10.4X5250</t>
+  </si>
+  <si>
+    <t>PVC SHEET PILE MA765X304X12X5500</t>
+  </si>
+  <si>
+    <t>PVC SHEET PILE MA765X280X10.4X5000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
-  </numFmts>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -164,7 +199,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -180,10 +215,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -486,1613 +523,2539 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I92"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:I122"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="28.28515625" customWidth="1"/>
-    <col min="2" max="2" width="37.7109375" customWidth="1"/>
-    <col min="3" max="3" width="31.28515625" customWidth="1"/>
+    <col min="1" max="1" width="28.26953125" customWidth="1"/>
+    <col min="2" max="2" width="37.7265625" customWidth="1"/>
+    <col min="3" max="3" width="31.26953125" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="32" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="36.140625" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" customWidth="1"/>
+    <col min="7" max="7" width="36.1796875" customWidth="1"/>
+    <col min="8" max="8" width="18.54296875" customWidth="1"/>
+    <col min="9" max="9" width="39.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="H1" s="1"/>
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
       <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
         <v>5000090945</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>1386</v>
       </c>
-      <c r="E3" s="1">
+      <c r="D3" s="1"/>
+      <c r="E3" s="3">
         <v>46133</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="3">
         <v>46139</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>1356</v>
       </c>
-      <c r="H3">
-        <f>C3-G3</f>
+      <c r="H3" s="1">
         <v>30</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
         <v>5000090927</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>462</v>
       </c>
-      <c r="E4" s="1">
+      <c r="D4" s="1"/>
+      <c r="E4" s="3">
         <v>46133</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="3">
         <v>46139</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>452</v>
       </c>
-      <c r="H4">
-        <f t="shared" ref="H4:H9" si="0">C4-G4</f>
+      <c r="H4" s="1">
         <v>10</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
         <v>5000090953</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>330</v>
       </c>
-      <c r="E5" s="1">
+      <c r="D5" s="1"/>
+      <c r="E5" s="3">
         <v>46140</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="3">
         <v>46190</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>310</v>
       </c>
-      <c r="H5">
-        <f t="shared" si="0"/>
+      <c r="H5" s="1">
         <v>20</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
         <v>5000090953</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>354</v>
       </c>
-      <c r="E6" s="1">
+      <c r="D6" s="1"/>
+      <c r="E6" s="3">
         <v>46176</v>
       </c>
-      <c r="I6" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7">
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
         <v>5000090956</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>462</v>
       </c>
-      <c r="E7" s="1">
+      <c r="D7" s="1"/>
+      <c r="E7" s="3">
         <v>46133</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="3">
         <v>46139</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>462</v>
       </c>
-      <c r="H7">
-        <f t="shared" si="0"/>
+      <c r="H7" s="1">
         <v>0</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
         <v>5000090956</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>156</v>
       </c>
-      <c r="E8" s="1">
+      <c r="D8" s="1"/>
+      <c r="E8" s="3">
         <v>46176</v>
       </c>
-      <c r="I8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9">
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
         <v>5000090956</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>972</v>
       </c>
-      <c r="E9" s="1">
+      <c r="D9" s="1"/>
+      <c r="E9" s="3">
         <v>46212</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10">
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
         <v>5000090956</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>1134</v>
       </c>
-      <c r="E10" s="1">
+      <c r="D10" s="1"/>
+      <c r="E10" s="3">
         <v>46221</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11">
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
         <v>5000091825</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>1716</v>
       </c>
-      <c r="E11" s="1">
+      <c r="D11" s="1"/>
+      <c r="E11" s="3">
         <v>46185</v>
       </c>
-      <c r="I11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12">
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
         <v>5000091825</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>788</v>
       </c>
-      <c r="E12" s="1">
+      <c r="D12" s="1"/>
+      <c r="E12" s="3">
         <v>46224</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13">
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>378</v>
       </c>
-      <c r="E13" s="1">
+      <c r="D13" s="1"/>
+      <c r="E13" s="3">
         <v>46140</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="3">
         <v>46190</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>378</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>0</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
-      <c r="A14">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>1512</v>
       </c>
-      <c r="E14" s="1">
+      <c r="D14" s="1"/>
+      <c r="E14" s="3">
         <v>46147</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="3">
         <v>46195</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>1512</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>0</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
-      <c r="A15">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>156</v>
       </c>
-      <c r="E15" s="1">
+      <c r="D15" s="1"/>
+      <c r="E15" s="3">
         <v>46150</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="3">
         <v>46192</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>156</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>0</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
-      <c r="A16">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>156</v>
       </c>
-      <c r="E16" s="1">
+      <c r="D16" s="1"/>
+      <c r="E16" s="3">
         <v>46155</v>
       </c>
-      <c r="I16" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
-      <c r="A17">
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>468</v>
       </c>
-      <c r="E17" s="1">
+      <c r="D17" s="1"/>
+      <c r="E17" s="3">
         <v>46161</v>
       </c>
-      <c r="I17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
-      <c r="A18">
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>1404</v>
       </c>
-      <c r="E18" s="1">
+      <c r="D18" s="1"/>
+      <c r="E18" s="3">
         <v>46164</v>
       </c>
-      <c r="I18" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19">
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>1716</v>
       </c>
-      <c r="E19" s="1">
+      <c r="D19" s="1"/>
+      <c r="E19" s="3">
         <v>46169</v>
       </c>
-      <c r="I19" t="s">
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
-      <c r="A20">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>936</v>
       </c>
-      <c r="E20" s="1">
+      <c r="D20" s="1"/>
+      <c r="E20" s="3">
         <v>46172</v>
       </c>
-      <c r="I20" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21">
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>2340</v>
       </c>
-      <c r="E21" s="1">
+      <c r="D21" s="1"/>
+      <c r="E21" s="3">
         <v>46176</v>
       </c>
-      <c r="I21" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
-      <c r="A22">
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>3432</v>
       </c>
-      <c r="E22" s="1">
+      <c r="D22" s="1"/>
+      <c r="E22" s="3">
         <v>46181</v>
       </c>
-      <c r="I22" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
-      <c r="A23">
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="1">
         <v>2652</v>
       </c>
-      <c r="E23" s="1">
+      <c r="D23" s="1"/>
+      <c r="E23" s="3">
         <v>46185</v>
       </c>
-      <c r="I23" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24">
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="1">
         <v>2184</v>
       </c>
-      <c r="E24" s="1">
+      <c r="D24" s="1"/>
+      <c r="E24" s="3">
         <v>46188</v>
       </c>
-      <c r="I24" t="s">
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
-      <c r="A25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="1">
         <v>5148</v>
       </c>
-      <c r="E25" s="1">
+      <c r="D25" s="1"/>
+      <c r="E25" s="3">
         <v>46197</v>
       </c>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26">
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>1620</v>
       </c>
-      <c r="E26" s="1">
+      <c r="D26" s="1"/>
+      <c r="E26" s="3">
         <v>46204</v>
       </c>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27">
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>2184</v>
       </c>
-      <c r="E27" s="1">
+      <c r="D27" s="1"/>
+      <c r="E27" s="3">
         <v>46206</v>
       </c>
-      <c r="I27" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
-      <c r="A28">
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>2592</v>
       </c>
-      <c r="E28" s="1">
+      <c r="D28" s="1"/>
+      <c r="E28" s="3">
         <v>46212</v>
       </c>
-    </row>
-    <row r="29" spans="1:9">
-      <c r="A29">
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>810</v>
       </c>
-      <c r="E29" s="1">
+      <c r="D29" s="1"/>
+      <c r="E29" s="3">
         <v>46224</v>
       </c>
-    </row>
-    <row r="30" spans="1:9">
-      <c r="A30">
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="1">
         <v>5000090952</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="1">
         <v>1296</v>
       </c>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31">
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="1">
         <v>5000090929</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="1">
         <v>308</v>
       </c>
-      <c r="E31" s="1">
+      <c r="D31" s="1"/>
+      <c r="E31" s="3">
         <v>46140</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="3">
         <v>46190</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="1">
         <v>308</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>0</v>
       </c>
-      <c r="I31" t="s">
+      <c r="I31" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
-      <c r="A32">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" s="1">
         <v>5000090929</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="1">
         <v>156</v>
       </c>
-      <c r="E32" s="1">
+      <c r="D32" s="1"/>
+      <c r="E32" s="3">
         <v>46150</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="3">
         <v>46192</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="1">
         <v>156</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>0</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
-      <c r="A33">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" s="1">
         <v>5000090929</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="1">
         <v>1620</v>
       </c>
-      <c r="E33" s="1">
+      <c r="D33" s="1"/>
+      <c r="E33" s="3">
         <v>46221</v>
       </c>
-    </row>
-    <row r="34" spans="1:9">
-      <c r="A34">
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" s="1">
         <v>5000090929</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="1">
         <v>1944</v>
       </c>
-      <c r="E34" s="1">
+      <c r="D34" s="1"/>
+      <c r="E34" s="3">
         <v>46224</v>
       </c>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35">
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" s="1">
         <v>5000090929</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="1">
         <v>810</v>
       </c>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36">
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" s="1">
         <v>5000091794</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B36" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="1">
         <v>162</v>
       </c>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37">
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37" s="1">
         <v>5000090928</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B37" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="1">
         <v>231</v>
       </c>
-      <c r="E37" s="1">
+      <c r="D37" s="1"/>
+      <c r="E37" s="3">
         <v>46176</v>
       </c>
-      <c r="I37" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38">
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A38" s="1">
         <v>5000090928</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B38" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="1">
         <v>2187</v>
       </c>
-      <c r="E38" s="1">
+      <c r="D38" s="1"/>
+      <c r="E38" s="3">
         <v>46181</v>
       </c>
-      <c r="I38" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39">
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A39" s="1">
         <v>5000090928</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B39" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="1">
         <v>13851</v>
       </c>
-      <c r="E39" s="1">
+      <c r="D39" s="1"/>
+      <c r="E39" s="3">
         <v>46185</v>
       </c>
-      <c r="I39" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40">
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A40" s="1">
         <v>5000090928</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B40" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="1">
         <v>8748</v>
       </c>
-      <c r="E40" s="1">
+      <c r="D40" s="1"/>
+      <c r="E40" s="3">
         <v>46188</v>
       </c>
-      <c r="I40" t="s">
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
-      <c r="A41">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A41" s="1">
         <v>5000090928</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B41" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="1">
         <v>25272</v>
       </c>
-      <c r="E41" s="1">
+      <c r="D41" s="1"/>
+      <c r="E41" s="3">
         <v>46197</v>
       </c>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42">
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A42" s="1">
         <v>5000090928</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B42" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="1">
         <v>8262</v>
       </c>
-      <c r="E42" s="1">
+      <c r="D42" s="1"/>
+      <c r="E42" s="3">
         <v>46204</v>
       </c>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43">
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A43" s="1">
         <v>5000090928</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B43" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="1">
         <v>1155</v>
       </c>
-      <c r="E43" s="1">
+      <c r="D43" s="1"/>
+      <c r="E43" s="3">
         <v>46206</v>
       </c>
-      <c r="I43" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44">
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A44" s="1">
         <v>5000090928</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B44" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="1">
         <v>19440</v>
       </c>
-      <c r="E44" s="1">
+      <c r="D44" s="1"/>
+      <c r="E44" s="3">
         <v>46212</v>
       </c>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45">
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A45" s="1">
         <v>5000090928</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="1">
         <v>29160</v>
       </c>
-      <c r="E45" s="1">
+      <c r="D45" s="1"/>
+      <c r="E45" s="3">
         <v>46221</v>
       </c>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="A46">
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A46" s="1">
         <v>5000090928</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B46" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="1">
         <v>33534</v>
       </c>
-      <c r="E46" s="1">
+      <c r="D46" s="1"/>
+      <c r="E46" s="3">
         <v>46224</v>
       </c>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47">
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A47" s="1">
         <v>5000090928</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B47" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="1">
         <v>25515</v>
       </c>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="B48" t="s">
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+      <c r="I47" s="1"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="1">
         <v>1315</v>
       </c>
-      <c r="E48" s="1">
+      <c r="D48" s="1"/>
+      <c r="E48" s="3">
         <v>46185</v>
       </c>
-      <c r="I48" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49">
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49" s="1">
         <v>5000090960</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="1">
         <v>378</v>
       </c>
-      <c r="E49" s="1">
+      <c r="D49" s="1"/>
+      <c r="E49" s="3">
         <v>46176</v>
       </c>
-      <c r="I49" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50">
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A50" s="1">
         <v>5000090960</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="1">
         <v>632</v>
       </c>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51">
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50" s="1"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A51" s="1">
         <v>5000090950</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B51" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="1">
         <v>745</v>
       </c>
-      <c r="E51" s="1">
+      <c r="D51" s="1"/>
+      <c r="E51" s="3">
         <v>46212</v>
       </c>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52">
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A52" s="1">
         <v>5000090950</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B52" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="1">
         <v>378</v>
       </c>
-      <c r="E52" s="1">
+      <c r="D52" s="1"/>
+      <c r="E52" s="3">
         <v>46221</v>
       </c>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53">
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A53" s="1">
         <v>5000090950</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B53" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="1">
         <v>756</v>
       </c>
-      <c r="E53" s="1">
+      <c r="D53" s="1"/>
+      <c r="E53" s="3">
         <v>46224</v>
       </c>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54">
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A54" s="1">
         <v>5000090957</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B54" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="1">
         <v>126</v>
       </c>
-      <c r="E54" s="1">
+      <c r="D54" s="1"/>
+      <c r="E54" s="3">
         <v>46155</v>
       </c>
-      <c r="I54" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55">
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A55" s="1">
         <v>5000090957</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B55" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="1">
         <v>882</v>
       </c>
-      <c r="E55" s="1">
+      <c r="D55" s="1"/>
+      <c r="E55" s="3">
         <v>46161</v>
       </c>
-      <c r="I55" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9">
-      <c r="A56">
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A56" s="1">
         <v>5000090957</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="1">
         <v>504</v>
       </c>
-      <c r="E56" s="1">
+      <c r="D56" s="1"/>
+      <c r="E56" s="3">
         <v>46164</v>
       </c>
-      <c r="I56" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9">
-      <c r="A57">
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A57" s="1">
         <v>5000090957</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B57" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="1">
         <v>919</v>
       </c>
-      <c r="E57" s="1">
+      <c r="D57" s="1"/>
+      <c r="E57" s="3">
         <v>46169</v>
       </c>
-      <c r="I57" t="s">
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
-      <c r="A58">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A58" s="1">
         <v>5000090957</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B58" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="1">
         <v>630</v>
       </c>
-      <c r="E58" s="1">
+      <c r="D58" s="1"/>
+      <c r="E58" s="3">
         <v>46172</v>
       </c>
-      <c r="I58" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9">
-      <c r="A59">
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A59" s="1">
         <v>5000090957</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B59" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="1">
         <v>378</v>
       </c>
-      <c r="E59" s="1">
+      <c r="D59" s="1"/>
+      <c r="E59" s="3">
         <v>46176</v>
       </c>
-      <c r="I59" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9">
-      <c r="A60">
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A60" s="1">
         <v>5000090957</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="1">
         <v>1134</v>
       </c>
-      <c r="E60" s="1">
+      <c r="D60" s="1"/>
+      <c r="E60" s="3">
         <v>46181</v>
       </c>
-      <c r="I60" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9">
-      <c r="A61">
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A61" s="1">
         <v>5000090957</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="1">
         <v>1638</v>
       </c>
-      <c r="E61" s="1">
+      <c r="D61" s="1"/>
+      <c r="E61" s="3">
         <v>46185</v>
       </c>
-      <c r="I61" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9">
-      <c r="A62">
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A62" s="1">
         <v>5000090957</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="1">
         <v>756</v>
       </c>
-      <c r="E62" s="1">
+      <c r="D62" s="1"/>
+      <c r="E62" s="3">
         <v>46188</v>
       </c>
-      <c r="I62" t="s">
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
-      <c r="A63">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A63" s="1">
         <v>5000090957</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="1">
         <v>2394</v>
       </c>
-      <c r="E63" s="1">
+      <c r="D63" s="1"/>
+      <c r="E63" s="3">
         <v>46197</v>
       </c>
-    </row>
-    <row r="64" spans="1:9">
-      <c r="A64">
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A64" s="1">
         <v>5000090957</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="1">
         <v>756</v>
       </c>
-      <c r="E64" s="1">
+      <c r="D64" s="1"/>
+      <c r="E64" s="3">
         <v>46204</v>
       </c>
-    </row>
-    <row r="65" spans="1:9">
-      <c r="A65">
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A65" s="1">
         <v>5000090957</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="1">
         <v>882</v>
       </c>
-      <c r="E65" s="1">
+      <c r="D65" s="1"/>
+      <c r="E65" s="3">
         <v>46206</v>
       </c>
-      <c r="I65" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9">
-      <c r="A66">
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A66" s="1">
         <v>5000090957</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="1">
         <v>767</v>
       </c>
-      <c r="E66" s="1">
+      <c r="D66" s="1"/>
+      <c r="E66" s="3">
         <v>46212</v>
       </c>
-    </row>
-    <row r="67" spans="1:9">
-      <c r="A67">
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A67" s="1">
         <v>5000090926</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="1">
         <v>252</v>
       </c>
-      <c r="E67" s="1">
+      <c r="D67" s="1"/>
+      <c r="E67" s="3">
         <v>46140</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67" s="3">
         <v>46190</v>
       </c>
-      <c r="G67">
+      <c r="G67" s="1">
         <v>252</v>
       </c>
-      <c r="H67">
+      <c r="H67" s="1">
         <v>0</v>
       </c>
-      <c r="I67" t="s">
+      <c r="I67" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
-      <c r="A68">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A68" s="1">
         <v>5000090926</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="1">
         <v>504</v>
       </c>
-      <c r="E68" s="1">
+      <c r="D68" s="1"/>
+      <c r="E68" s="3">
         <v>46147</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68" s="3">
         <v>46195</v>
       </c>
-      <c r="G68">
+      <c r="G68" s="1">
         <v>504</v>
       </c>
-      <c r="H68">
+      <c r="H68" s="1">
         <v>0</v>
       </c>
-      <c r="I68" t="s">
+      <c r="I68" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
-      <c r="A69">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A69" s="1">
         <v>5000090926</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="1">
         <v>252</v>
       </c>
-      <c r="E69" s="1">
+      <c r="D69" s="1"/>
+      <c r="E69" s="3">
         <v>46150</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69" s="3">
         <v>46192</v>
       </c>
-      <c r="G69">
+      <c r="G69" s="1">
         <v>252</v>
       </c>
-      <c r="H69">
+      <c r="H69" s="1">
         <v>0</v>
       </c>
-      <c r="I69" t="s">
+      <c r="I69" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
-      <c r="A70">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A70" s="1">
         <v>5000090926</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="1">
         <v>504</v>
       </c>
-      <c r="E70" s="1">
+      <c r="D70" s="1"/>
+      <c r="E70" s="3">
         <v>46155</v>
       </c>
-      <c r="I70" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9">
-      <c r="B71" t="s">
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="1">
         <v>1638</v>
       </c>
-    </row>
-    <row r="72" spans="1:9">
-      <c r="A72">
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A72" s="1">
         <v>5000090955</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="1">
         <v>540</v>
       </c>
-      <c r="E72" s="1">
+      <c r="D72" s="1"/>
+      <c r="E72" s="3">
         <v>46212</v>
       </c>
-    </row>
-    <row r="73" spans="1:9">
-      <c r="A73">
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A73" s="1">
         <v>5000090955</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="1">
         <v>540</v>
       </c>
-      <c r="E73" s="1">
+      <c r="D73" s="1"/>
+      <c r="E73" s="3">
         <v>46221</v>
       </c>
-    </row>
-    <row r="74" spans="1:9">
-      <c r="A74">
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A74" s="1">
         <v>5000090954</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="1">
         <v>296</v>
       </c>
-      <c r="E74" s="1">
+      <c r="D74" s="1"/>
+      <c r="E74" s="3">
         <v>46185</v>
       </c>
-      <c r="I74" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9">
-      <c r="A75">
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A75" s="1">
         <v>5000090954</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="1">
         <v>756</v>
       </c>
-      <c r="E75" s="1">
+      <c r="D75" s="1"/>
+      <c r="E75" s="3">
         <v>46188</v>
       </c>
-      <c r="I75" t="s">
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
-      <c r="A76">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A76" s="1">
         <v>5000090954</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="1">
         <v>2916</v>
       </c>
-      <c r="E76" s="1">
+      <c r="D76" s="1"/>
+      <c r="E76" s="3">
         <v>46197</v>
       </c>
-    </row>
-    <row r="77" spans="1:9">
-      <c r="A77">
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A77" s="1">
         <v>5000090954</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="1">
         <v>1188</v>
       </c>
-      <c r="E77" s="1">
+      <c r="D77" s="1"/>
+      <c r="E77" s="3">
         <v>46204</v>
       </c>
-    </row>
-    <row r="78" spans="1:9">
-      <c r="A78">
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A78" s="1">
         <v>5000090954</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="1">
         <v>106</v>
       </c>
-      <c r="E78" s="1">
+      <c r="D78" s="1"/>
+      <c r="E78" s="3">
         <v>46212</v>
       </c>
-    </row>
-    <row r="79" spans="1:9">
-      <c r="A79">
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A79" s="1">
         <v>5000090951</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="1">
         <v>635</v>
       </c>
-      <c r="E79" s="1">
+      <c r="D79" s="1"/>
+      <c r="E79" s="3">
         <v>46133</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F79" s="3">
         <v>46139</v>
       </c>
-      <c r="G79">
+      <c r="G79" s="1">
         <v>635</v>
       </c>
-      <c r="H79">
+      <c r="H79" s="1">
         <v>0</v>
       </c>
-      <c r="I79" t="s">
+      <c r="I79" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
-      <c r="A80">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A80" s="1">
         <v>5000090951</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="1">
         <v>540</v>
       </c>
-      <c r="E80" s="1">
+      <c r="D80" s="1"/>
+      <c r="E80" s="3">
         <v>46140</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80" s="3">
         <v>46190</v>
       </c>
-      <c r="G80">
+      <c r="G80" s="1">
         <v>540</v>
       </c>
-      <c r="H80">
+      <c r="H80" s="1">
         <v>0</v>
       </c>
-      <c r="I80" t="s">
+      <c r="I80" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
-      <c r="A81">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81" s="1">
         <v>5000090951</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="1">
         <v>864</v>
       </c>
-      <c r="E81" s="1">
+      <c r="D81" s="1"/>
+      <c r="E81" s="3">
         <v>46147</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81" s="3">
         <v>46195</v>
       </c>
-      <c r="G81">
+      <c r="G81" s="1">
         <v>864</v>
       </c>
-      <c r="H81">
+      <c r="H81" s="1">
         <v>0</v>
       </c>
-      <c r="I81" t="s">
+      <c r="I81" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
-      <c r="A82">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82" s="1">
         <v>5000090951</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="1">
         <v>642</v>
       </c>
-      <c r="E82" s="1">
+      <c r="D82" s="1"/>
+      <c r="E82" s="3">
         <v>46150</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82" s="3">
         <v>46192</v>
       </c>
-      <c r="G82">
+      <c r="G82" s="1">
         <v>642</v>
       </c>
-      <c r="H82">
+      <c r="H82" s="1">
         <v>0</v>
       </c>
-      <c r="I82" t="s">
+      <c r="I82" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
-      <c r="A83">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A83" s="1">
         <v>5000090951</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="1">
         <v>642</v>
       </c>
-      <c r="E83" s="1">
+      <c r="D83" s="1"/>
+      <c r="E83" s="3">
         <v>46155</v>
       </c>
-      <c r="I83" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9">
-      <c r="A84">
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84" s="1">
         <v>5000090951</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="1">
         <v>1074</v>
       </c>
-      <c r="E84" s="1">
+      <c r="D84" s="1"/>
+      <c r="E84" s="3">
         <v>46161</v>
       </c>
-      <c r="I84" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9">
-      <c r="A85">
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A85" s="1">
         <v>5000090951</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="1">
         <v>540</v>
       </c>
-      <c r="E85" s="1">
+      <c r="D85" s="1"/>
+      <c r="E85" s="3">
         <v>46164</v>
       </c>
-      <c r="I85" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9">
-      <c r="A86">
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A86" s="1">
         <v>5000090951</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="1">
         <v>642</v>
       </c>
-      <c r="E86" s="1">
+      <c r="D86" s="1"/>
+      <c r="E86" s="3">
         <v>46169</v>
       </c>
-      <c r="I86" t="s">
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
-      <c r="A87">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A87" s="1">
         <v>5000090951</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B87" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="1">
         <v>1368</v>
       </c>
-      <c r="E87" s="1">
+      <c r="D87" s="1"/>
+      <c r="E87" s="3">
         <v>46172</v>
       </c>
-      <c r="I87" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9">
-      <c r="A88">
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A88" s="1">
         <v>5000090951</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B88" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="1">
         <v>1080</v>
       </c>
-      <c r="E88" s="1">
+      <c r="D88" s="1"/>
+      <c r="E88" s="3">
         <v>46176</v>
       </c>
-      <c r="I88" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9">
-      <c r="A89">
+      <c r="F88" s="1"/>
+      <c r="G88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="I88" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A89" s="1">
         <v>5000090951</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B89" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="1">
         <v>972</v>
       </c>
-      <c r="E89" s="1">
+      <c r="D89" s="1"/>
+      <c r="E89" s="3">
         <v>46181</v>
       </c>
-      <c r="I89" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9">
-      <c r="A90">
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A90" s="1">
         <v>5000090951</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="1">
         <v>1410</v>
       </c>
-      <c r="E90" s="1">
+      <c r="D90" s="1"/>
+      <c r="E90" s="3">
         <v>46185</v>
       </c>
-      <c r="I90" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9">
-      <c r="A91">
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A91" s="1">
         <v>5000090951</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C91">
+      <c r="C91" s="1">
         <v>324</v>
       </c>
-      <c r="E91" s="1">
+      <c r="D91" s="1"/>
+      <c r="E91" s="3">
         <v>46206</v>
       </c>
-      <c r="I91" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9">
-      <c r="A92">
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A92" s="1">
         <v>5000090951</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="1">
         <v>1082</v>
       </c>
-      <c r="E92" s="1">
+      <c r="D92" s="1"/>
+      <c r="E92" s="3">
         <v>46212</v>
       </c>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A93" s="1">
+        <v>5000088682</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C93" s="4">
+        <v>1915</v>
+      </c>
+      <c r="D93" s="1"/>
+      <c r="E93" s="1"/>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A94" s="1">
+        <v>5000088682</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C94" s="4">
+        <v>2000</v>
+      </c>
+      <c r="D94" s="1"/>
+      <c r="E94" s="1"/>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A95" s="1">
+        <v>5000088682</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C95" s="4">
+        <v>6870</v>
+      </c>
+      <c r="D95" s="1"/>
+      <c r="E95" s="1"/>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A96" s="1">
+        <v>5000088682</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C96" s="4">
+        <v>5000</v>
+      </c>
+      <c r="D96" s="1"/>
+      <c r="E96" s="1"/>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A97" s="1">
+        <v>5000090928</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C97" s="4">
+        <v>12879</v>
+      </c>
+      <c r="D97" s="1"/>
+      <c r="E97" s="1"/>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A98" s="1">
+        <v>5000090928</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C98" s="4">
+        <v>12393</v>
+      </c>
+      <c r="D98" s="1"/>
+      <c r="E98" s="1"/>
+      <c r="F98" s="1"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A99" s="1">
+        <v>5000090929</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C99" s="1">
+        <v>972</v>
+      </c>
+      <c r="D99" s="1"/>
+      <c r="E99" s="1"/>
+      <c r="F99" s="1"/>
+      <c r="G99" s="1"/>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A100" s="1">
+        <v>5000090929</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C100" s="1">
+        <v>162</v>
+      </c>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A101" s="1">
+        <v>5000090950</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C101" s="1">
+        <v>755</v>
+      </c>
+      <c r="D101" s="1"/>
+      <c r="E101" s="1"/>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
+      <c r="H101" s="1"/>
+      <c r="I101" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A102" s="1">
+        <v>5000090952</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" s="1">
+        <v>972</v>
+      </c>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A103" s="1">
+        <v>5000090952</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C103" s="1">
+        <v>486</v>
+      </c>
+      <c r="D103" s="1"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
+      <c r="H103" s="1"/>
+      <c r="I103" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A104" s="1">
+        <v>5000091439</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C104" s="1">
+        <v>668</v>
+      </c>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A105" s="1">
+        <v>5000091439</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C105" s="1">
+        <v>840</v>
+      </c>
+      <c r="D105" s="1"/>
+      <c r="E105" s="1"/>
+      <c r="F105" s="1"/>
+      <c r="G105" s="1"/>
+      <c r="H105" s="1"/>
+      <c r="I105" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A106" s="1">
+        <v>5000091439</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C106" s="1">
+        <v>840</v>
+      </c>
+      <c r="D106" s="1"/>
+      <c r="E106" s="1"/>
+      <c r="F106" s="1"/>
+      <c r="G106" s="1"/>
+      <c r="H106" s="1"/>
+      <c r="I106" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A107" s="1">
+        <v>5000091439</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C107" s="1">
+        <v>840</v>
+      </c>
+      <c r="D107" s="1"/>
+      <c r="E107" s="1"/>
+      <c r="F107" s="1"/>
+      <c r="G107" s="1"/>
+      <c r="H107" s="1"/>
+      <c r="I107" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A108" s="1">
+        <v>5000091439</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C108" s="4">
+        <v>1680</v>
+      </c>
+      <c r="D108" s="1"/>
+      <c r="E108" s="1"/>
+      <c r="F108" s="1"/>
+      <c r="G108" s="1"/>
+      <c r="H108" s="1"/>
+      <c r="I108" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A109" s="1">
+        <v>5000091460</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C109" s="1">
+        <v>528</v>
+      </c>
+      <c r="D109" s="1"/>
+      <c r="E109" s="1"/>
+      <c r="F109" s="1"/>
+      <c r="G109" s="1"/>
+      <c r="H109" s="1"/>
+      <c r="I109" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A110" s="1">
+        <v>5000091460</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C110" s="1">
+        <v>880</v>
+      </c>
+      <c r="D110" s="1"/>
+      <c r="E110" s="1"/>
+      <c r="F110" s="1"/>
+      <c r="G110" s="1"/>
+      <c r="H110" s="1"/>
+      <c r="I110" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A111" s="1">
+        <v>5000091460</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C111" s="1">
+        <v>704</v>
+      </c>
+      <c r="D111" s="1"/>
+      <c r="E111" s="1"/>
+      <c r="F111" s="1"/>
+      <c r="G111" s="1"/>
+      <c r="H111" s="1"/>
+      <c r="I111" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A112" s="1">
+        <v>5000091460</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C112" s="4">
+        <v>1936</v>
+      </c>
+      <c r="D112" s="1"/>
+      <c r="E112" s="1"/>
+      <c r="F112" s="1"/>
+      <c r="G112" s="1"/>
+      <c r="H112" s="1"/>
+      <c r="I112" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A113" s="1">
+        <v>5000091460</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C113" s="1">
+        <v>176</v>
+      </c>
+      <c r="D113" s="1"/>
+      <c r="E113" s="1"/>
+      <c r="F113" s="1"/>
+      <c r="G113" s="1"/>
+      <c r="H113" s="1"/>
+      <c r="I113" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A114" s="1">
+        <v>5000091461</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C114" s="1">
+        <v>672</v>
+      </c>
+      <c r="D114" s="1"/>
+      <c r="E114" s="1"/>
+      <c r="F114" s="1"/>
+      <c r="G114" s="1"/>
+      <c r="H114" s="1"/>
+      <c r="I114" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A115" s="1">
+        <v>5000091461</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C115" s="1">
+        <v>840</v>
+      </c>
+      <c r="D115" s="1"/>
+      <c r="E115" s="1"/>
+      <c r="F115" s="1"/>
+      <c r="G115" s="1"/>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A116" s="1">
+        <v>5000091461</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C116" s="1">
+        <v>840</v>
+      </c>
+      <c r="D116" s="1"/>
+      <c r="E116" s="1"/>
+      <c r="F116" s="1"/>
+      <c r="G116" s="1"/>
+      <c r="H116" s="1"/>
+      <c r="I116" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A117" s="1">
+        <v>5000091461</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C117" s="1">
+        <v>840</v>
+      </c>
+      <c r="D117" s="1"/>
+      <c r="E117" s="1"/>
+      <c r="F117" s="1"/>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A118" s="1">
+        <v>5000091461</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C118" s="1">
+        <v>168</v>
+      </c>
+      <c r="D118" s="1"/>
+      <c r="E118" s="1"/>
+      <c r="F118" s="1"/>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
+      <c r="I118" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A119" s="1">
+        <v>5000091470</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C119" s="1">
+        <v>880</v>
+      </c>
+      <c r="D119" s="1"/>
+      <c r="E119" s="1"/>
+      <c r="F119" s="1"/>
+      <c r="G119" s="1"/>
+      <c r="H119" s="1"/>
+      <c r="I119" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A120" s="1">
+        <v>5000091470</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C120" s="1">
+        <v>968</v>
+      </c>
+      <c r="D120" s="1"/>
+      <c r="E120" s="1"/>
+      <c r="F120" s="1"/>
+      <c r="G120" s="1"/>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A121" s="1">
+        <v>5000091470</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C121" s="1">
+        <v>968</v>
+      </c>
+      <c r="D121" s="1"/>
+      <c r="E121" s="1"/>
+      <c r="F121" s="1"/>
+      <c r="G121" s="1"/>
+      <c r="H121" s="1"/>
+      <c r="I121" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A122" s="1">
+        <v>5000091794</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C122" s="1">
+        <v>810</v>
+      </c>
+      <c r="D122" s="1"/>
+      <c r="E122" s="1"/>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I92" xr:uid="{B679BF15-5756-42AF-A8C1-3FF5B05AED4D}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2100,87 +3063,87 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B088DB1E-FEB8-428B-9DA8-69DDD53FA0D4}">
   <dimension ref="B5:B21"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="28.5703125" customWidth="1"/>
+    <col min="2" max="2" width="28.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:2">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>5000090945</v>
       </c>
     </row>
-    <row r="6" spans="2:2">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>5000090927</v>
       </c>
     </row>
-    <row r="7" spans="2:2">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>5000090953</v>
       </c>
     </row>
-    <row r="8" spans="2:2">
+    <row r="8" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>5000090956</v>
       </c>
     </row>
-    <row r="9" spans="2:2">
+    <row r="9" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>5000091825</v>
       </c>
     </row>
-    <row r="10" spans="2:2">
+    <row r="10" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>5000090952</v>
       </c>
     </row>
-    <row r="11" spans="2:2">
+    <row r="11" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>5000090929</v>
       </c>
     </row>
-    <row r="12" spans="2:2">
+    <row r="12" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B12">
         <v>5000091794</v>
       </c>
     </row>
-    <row r="13" spans="2:2">
+    <row r="13" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B13">
         <v>5000090928</v>
       </c>
     </row>
-    <row r="15" spans="2:2">
+    <row r="15" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B15">
         <v>5000090960</v>
       </c>
     </row>
-    <row r="16" spans="2:2">
+    <row r="16" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B16">
         <v>5000090950</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>5000090957</v>
       </c>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>5000090926</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>5000090955</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B20">
         <v>5000090954</v>
       </c>
     </row>
-    <row r="21" spans="2:2">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B21">
         <v>5000090951</v>
       </c>
